--- a/Resultado de Jsons..xlsx
+++ b/Resultado de Jsons..xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,22 +478,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FERTILIZANTES DE C.A. (EL SALVADOR), S.A.</t>
+          <t>MERCADOS ELECTRICOS DE CENTROAMERICA, S.A. DE C.V.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>23EC9A36-9070-4AF6-8356-9734A966E390</t>
+          <t>0178483A-CC0C-406B-8D75-56A23E141CDF</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>202504CA1DB48A3E460C8D68FEBF3F8C45AAATBG</t>
+          <t>2025DA6943E63D04476E815D9A4466C1CD8EPWYK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -503,42 +503,42 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DTE-07-M001P001-000000000002286</t>
+          <t>DTE-07-M001P000-000000000000223</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>B5558F60-5110-4DFD-A546-49411537A94B</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8.4</v>
+        <v>3.81</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>23EC9A36-9070-4AF6-8356-9734A966E390.json</t>
+          <t>0178483A-CC0C-406B-8D75-56A23E141CDF.json</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Textiles San Andres S.A. de C.V.</t>
+          <t>TEXTUFIL, S.A. DE C.V.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3BBBC531-145B-454A-AB1C-152909354012</t>
+          <t>08C47A1E-489B-4747-96BF-BDBA13D427F9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20251824270FF30B4BCAB26C3FA8D3BB3A4ADFUF</t>
+          <t>2025ED929EB9BE9845348BB99A513583D61ANJSL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -548,42 +548,42 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DTE-07-M001P001-000000000001974</t>
+          <t>DTE-07-M001P029-000000000006599</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DB34B2A4-4743-472A-88A0-AA6B89F7F643</t>
+          <t>29067140-6E1C-4CF1-A85D-ABFD8EC8A752</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4.35</v>
+        <v>7.92</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3BBBC531-145B-454A-AB1C-152909354012.json</t>
+          <t>08C47A1E-489B-4747-96BF-BDBA13D427F9.json</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rayones de El Salvador S.A. de C.V.</t>
+          <t>TEXTUFIL, S.A. DE C.V.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5261228E-5188-4F4C-8D03-B83CB26DFF85</t>
+          <t>08C47A1E-489B-4747-96BF-BDBA13D427F9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>202563AC26410D804A3AA5971C17DBE42EEB4AFH</t>
+          <t>2025ED929EB9BE9845348BB99A513583D61ANJSL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -593,42 +593,42 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DTE-07-M001P004-000000000001434</t>
+          <t>DTE-07-M001P029-000000000006599</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FD7D485B-B79D-451F-A783-5E07742FAA0E</t>
+          <t>4619C8C6-F2CA-4422-96D0-4C0871F42D84</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.390000000000001</v>
+        <v>7.92</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5261228E-5188-4F4C-8D03-B83CB26DFF85.json</t>
+          <t>08C47A1E-489B-4747-96BF-BDBA13D427F9.json</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PRODUCTOS ALIMENTICIOS DIANA, S.A. DE C.V.</t>
+          <t>MEDRANO FLORES, S.A. DE C.V.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>895CC853-0876-4691-B51C-35E1339AE1AD</t>
+          <t>09C6487E-B719-434C-BBFE-CC60313942DB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025ED31114D32D54222BCF7683FB9CC90B9A0BV</t>
+          <t>202508812CC173764A45806596647361F98DSBI2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -638,42 +638,42 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DTE-07-M001P011-000000000013644</t>
+          <t>DTE-07-M001P001-000000000006493</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3C0C241F-BE71-45DC-B80E-EF767F27E4E0</t>
+          <t>649AAA12-D3CD-4B85-A5D7-F590AA9BEE26</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.79</v>
+        <v>6.45</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>895CC853-0876-4691-B51C-35E1339AE1AD.json</t>
+          <t>09C6487E-B719-434C-BBFE-CC60313942DB.json</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PRODUCTOS ALIMENTICIOS BOCADELI, S.A. DE C.V.</t>
+          <t>CENTRAL DE RODAMIENTOS, S.A. DE C.V.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A64EB72E-2966-47A1-B24F-30432BE35683</t>
+          <t>115BBDE7-2265-4FDD-8DA9-4D7FBCB8E58F</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>202523F067937D5342648810FA3F2104AFA5FQWK</t>
+          <t>20256F673605590048C5B6716C1CBB0388BE17CQ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -683,42 +683,36 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DTE-07-M001P026-000000000006613</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>DTE-7951</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>11.91</v>
-      </c>
+          <t>DTE-05-M001P001-000000000000372</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>A64EB72E-2966-47A1-B24F-30432BE35683.json</t>
+          <t>115BBDE7-2265-4FDD-8DA9-4D7FBCB8E58F.json</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KIMBERLY-CLARK DE CENTROAMERICA, LIMITAD</t>
+          <t>Lacteos del Corral, S.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0050569F-D919-1FD0-B48F-EF77A256A0E7</t>
+          <t>13B5D334-13CE-48AD-AE24-7D8497D38E32</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20259649C2A6BC8541489960D90C577EDFAEFAPN</t>
+          <t>2025B23AD78557A94C869D359AFFA7B2F692KFVB</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -728,42 +722,42 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>DTE-07-M001P001-000000000006092</t>
+          <t>DTE-07-S001P001-000000000006634</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DTE03M001007536</t>
+          <t>DTE-03-7005</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5.3</v>
+        <v>2.23</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Comprobante de Retención_6092_KIMBERLY-CLARK DE CENTROAMERICA, LIMITAD.json</t>
+          <t>13B5D334-13CE-48AD-AE24-7D8497D38E32.json</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FERTILIZANTES DE C.A. (EL SALVADOR), S.A.</t>
+          <t>TEXTUFIL, S.A. DE C.V.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>D594791E-4B19-4FF2-8219-15FD3789D353</t>
+          <t>1BF1D241-813E-4BBC-9FE0-2B56E2176DC3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20258D62068E05B34327B2AA2A160B9E1AA5X8T1</t>
+          <t>202544F4EF8ACB424B5483500A4B072F5B6DNVWA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -773,223 +767,3905 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>DTE-07-M001P001-000000000002287</t>
+          <t>DTE-07-M001P029-000000000006581</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>DEEDE031-6E93-4126-86FD-9D8674197606</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>122.74</v>
+        <v>8.4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D594791E-4B19-4FF2-8219-15FD3789D353.json</t>
+          <t>1BF1D241-813E-4BBC-9FE0-2B56E2176DC3.json</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Empaques y Sabores S.A de C.V</t>
+          <t>TEXTUFIL, S.A. DE C.V.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>D972B97D-329F-4899-A965-631A284D7031</t>
+          <t>1BF1D241-813E-4BBC-9FE0-2B56E2176DC3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20253A2823E17C05458D8863C9083BAD0A61GBLA</t>
+          <t>202544F4EF8ACB424B5483500A4B072F5B6DNVWA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>responseMH -&gt; selloRecibido</t>
+          <t>selloRecibido</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DTE-07-M001P001-000000000001187</t>
+          <t>DTE-07-M001P029-000000000006581</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DTE-03-M001P001-000000000007708</t>
+          <t>10DED517-2642-4652-885D-E77893A2CF63</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>8.4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>D972B97D-329F-4899-A965-631A284D7031.json</t>
+          <t>1BF1D241-813E-4BBC-9FE0-2B56E2176DC3.json</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TEXTUFIL, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1BF1D241-813E-4BBC-9FE0-2B56E2176DC3</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025D87201CF41DC42259EFC36C4C1890155AUFN</t>
+          <t>202544F4EF8ACB424B5483500A4B072F5B6DNVWA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SelloRecibido</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P029-000000000006581</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>C6A3ED21-0AF7-4742-81DC-E2DF4231546A</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>8.4</v>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>DTE-07-M001P001-000000000000455.json</t>
+          <t>1BF1D241-813E-4BBC-9FE0-2B56E2176DC3.json</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INDUSTRIAS SINTENTICAS DE CENTRO AMERICA, S.A.</t>
+          <t>CENTRAL DE RODAMIENTOS, S.A. DE C.V.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2098F044-A12C-4647-A97B-E62004067E29</t>
+          <t>1C06FFA3-07CE-4F9A-94AF-6611F75A4EA7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>eyJhbGciOiJSUzUxMiJ9.ewogICJpZGVudGlmaWNhY2lvbiIgOiB7CiAgICAidmVyc2lvbiIgOiAxLAogICAgImFtYmllbnRlIiA6ICIwMSIsCiAgICAidGlwb0R0ZSIgOiAiMDciLAogICAgIm51bWVyb0NvbnRyb2wiIDogIkRURS0wNy1NMDAxUDAwMS0wMDAwMDAwMDAwMDE4ODEiLAogICAgImNvZGlnb0dlbmVyYWNpb24iIDogIjIwOThGMDQ0LUExMkMtNDY0Ny1BOTdCLUU2MjAwNDA2N0UyOSIsCiAgICAidGlwb01vZGVsbyIgOiAxLAogICAgInRpcG9PcGVyYWNpb24iIDogMSwKICAgICJ0aXBvQ29udGluZ2VuY2lhIiA6IG51bGwsCiAgICAibW90aXZvQ29udGluIiA6IG51bGwsCiAgICAiZmVjRW1pIiA6ICIyMDI1LTExLTI4IiwKICAgICJob3JFbWkiIDogIjE1OjM2OjE5IiwKICAgICJ0aXBvTW9uZWRhIiA6ICJVU0QiCiAgfSwKICAiZW1pc29yIiA6IHsKICAgICJuaXQiIDogIjA2MTQyNjA1NjYwMDEzIiwKICAgICJucmMiIDogIjQ2NTAiLAogICAgIm5vbWJyZSIgOiAiSU5EVVNUUklBUyBTSU5URU5USUNBUyBERSBDRU5UUk8gQU1FUklDQSwgUy5BLiIsCiAgICAiY29kQWN0aXZpZGFkIiA6ICIxMzEyMCIsCiAgICAiZGVzY0FjdGl2aWRhZCIgOiAiRmFicmljYWNpw7NuIGRlIHRlbGFzIiwKICAgICJub21icmVDb21lcmNpYWwiIDogIklOU0lOQ0EsIFMuQS4iLAogICAgInRpcG9Fc3RhYmxlY2ltaWVudG8iIDogIjAyIiwKICAgICJkaXJlY2Npb24iIDogewogICAgICAiZGVwYXJ0YW1lbnRvIiA6ICIwNiIsCiAgICAgICJtdW5pY2lwaW8iIDogIjIxIiwKICAgICAgImNvbXBsZW1lbnRvIiA6ICJLSUxPTUVUUk8gMTLCvSBDQVJSRVRFUkEgVFJPTkNBTCBERUwgTk9SVEUsIFNBTiBTQUxWQURPUiBPRVNURSwgU0FOIFNBTFZBRE9SIgogICAgfSwKICAgICJ0ZWxlZm9ubyIgOiAiMjIxNjAwNTUiLAogICAgImNvZGlnb01IIiA6ICJNMDAxIiwKICAgICJjb2RpZ28iIDogbnVsbCwKICAgICJwdW50b1ZlbnRhTUgiIDogIlAwMDEiLAogICAgInB1bnRvVmVudGEiIDogbnVsbCwKICAgICJjb3JyZW8iIDogImZhY3R1cmFlLmluc2luY2FAaW5zaW5jYS5jb20iCiAgfSwKICAicmVjZXB0b3IiIDogewogICAgInRpcG9Eb2N1bWVudG8iIDogIjM2IiwKICAgICJudW1Eb2N1bWVudG8iIDogIjA2MTQxNTExNzcwMDIwIiwKICAgICJucmMiIDogIjE2MTI4IiwKICAgICJub21icmUiIDogIkNFTlRSQUwgREUgUk9EQU1JRU5UT1MgUy5BIERFIEMuVi4iLAogICAgImNvZEFjdGl2aWRhZCIgOiAiNDY1OTkiLAogICAgImRlc2NBY3RpdmlkYWQiIDogIlZlbnRhIGFsIHBvciAgbWF5b3IgZGUgb3RybyB0aXBvIGRlIG1hcXVpbmFyaWEgeSBlcXVpcG8gY29uIHN1cyBhY2Nlc29yaW9zIHkgcGFydGVzIiwKICAgICJub21icmVDb21lcmNpYWwiIDogIkNFTlRSQUwgREUgUk9EQU1JRU5UT1MgUy5BIERFIEMuVi4iLAogICAgImRpcmVjY2lvbiIgOiB7CiAgICAgICJkZXBhcnRhbWVudG8iIDogIjA2IiwKICAgICAgIm11bmljaXBpbyIgOiAiMjMiLAogICAgICAiY29tcGxlbWVudG8iIDogIkJMVkQuIFZFTkVaVUVMQSAjMzA3NyBTYW4gU2FsdmFkb3IgQ2VudHJvIgogICAgfSwKICAgICJ0ZWxlZm9ubyIgOiBudWxsLAogICAgImNvcnJlbyIgOiAicmF1bC5ndWV2YXJhQGNlcm9zYS5jb20iCiAgfSwKICAiY3VlcnBvRG9jdW1lbnRvIiA6IFsgewogICAgIm51bUl0ZW0iIDogMSwKICAgICJ0aXBvRHRlIiA6ICIwMyIsCiAgICAidGlwb0RvYyIgOiAyLAogICAgIm51bURvY3VtZW50byIgOiAiRUY0MUU3MEEtNUI3RS00MUM1LTkxNTctODRCOTlBRjk2MkNDIiwKICAgICJmZWNoYUVtaXNpb24iIDogIjIwMjUtMTEtMjYiLAogICAgIm1vbnRvU3VqZXRvR3JhdiIgOiAyMjAsCiAgICAiY29kaWdvUmV0ZW5jaW9uTUgiIDogIjIyIiwKICAgICJpdmFSZXRlbmlkbyIgOiAyLjIsCiAgICAiZGVzY3JpcGNpb24iIDogIkRURSAgIDc3MzggICAgIDI2LTExLTIwMjUgQ1IgIyA0NTk0IgogIH0gXSwKICAicmVzdW1lbiIgOiB7CiAgICAidG90YWxTdWpldG9SZXRlbmNpb24iIDogMjIwLAogICAgInRvdGFsSVZBcmV0ZW5pZG8iIDogMi4yLAogICAgInRvdGFsSVZBcmV0ZW5pZG9MZXRyYXMiIDogIkRPUyAyMC8xMDAgRE9MQVJFUyIKICB9LAogICJleHRlbnNpb24iIDogbnVsbCwKICAiYXBlbmRpY2UiIDogWyB7CiAgICAiY2FtcG8iIDogIk4uUmV0LiIsCiAgICAiZXRpcXVldGEiIDogImNvcnJlbGF0aXZvIiwKICAgICJ2YWxvciIgOiAiWiA0NTk0IgogIH0sIHsKICAgICJjYW1wbyIgOiAiRWxhYm9yYWRvIFBvcjoiLAogICAgImV0aXF1ZXRhIiA6ICJkaWdpdGFkb3IiLAogICAgInZhbG9yIiA6ICJKT1NTRUxJTk5FIEJBUkFIT05BIgogIH0gXQp9.kGrmA9S3thhBUysM4O8MHfhfS8RzALhwRbZqbef-dCL2J_PK9PWBZC8juvRylwtBNi8LFhHDzfnUCg6nMMYl4uO6JCPwqJwajaadpqF_4WmNY4WG9CHubIC2btYHXCNbBzE-VwJkMFpPmxSgP-hllyf1-A5Nn2RxR2hg7R1BA1pblJQc15b9Fk-iJDhZP180LjqoXvA4HFckaxoKDDiuT7YLlDLEjG5Lyv5pns6QAx3mqs_lmEmS30demqJVKB0sHTsB7wgYhLRvBbGdj6zkMN6JZL0yskYU9WMoOyozBNNUe4kZMT2PR3bU_p9Wn_8Xz4EmW6HqXHYireWN2yxCAA</t>
+          <t>2025F97DE03E6EBD4D9686F24B0EAA1720FDTJQT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>acuseMH -&gt; firma</t>
+          <t>selloRecibido</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DTE-07-M001P001-000000000001881</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EF41E70A-5B7E-41C5-9157-84B99AF962CC</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>2.2</v>
-      </c>
+          <t>DTE-03-M001P001-000000000007703</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DTE-07-M001P001-000000000001881_2098f044-a12c-4647-a97b-e62004067e29.json</t>
+          <t>1C06FFA3-07CE-4F9A-94AF-6611F75A4EA7.json</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PLYCEM CONSTRUSISTEMAS EL SALVADOR, S.A. DE C.V.</t>
+          <t>Unilever El Salvador SCC S.A. de C.V.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0EBE3379-5203-1FE0-ADD3-740CCEDA8FC5</t>
+          <t>0C97B2C2-ADA4-4BCE-AC4A-7782C054B934</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>202582E9F7AFD9E34DCC85123083F97BB14DORL2</t>
+          <t>20255F5001DD353D4A9B895B4226818D296A4DVW</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>responseMH -&gt; selloRecibido</t>
+          <t>selloRecibido</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DTE-07-M001P000-000000000002115</t>
+          <t>DTE-07-M001P000-202500000007514</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>DTE-03-M001P001-000000000006470</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>50.02</v>
+        <v>21.15</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Plycem_5100010374_2025.json</t>
+          <t>1P001-00000000000647006141511770020.json</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PLYCEM CONSTRUSISTEMAS EL SALVADOR, S.A. DE C.V.</t>
+          <t>Unilever El Salvador SCC S.A. de C.V.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>C197E463-C660-4465-AAE6-5A55365ADB6C</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>20253B620E839C1C4910AB0D7AEEFEC72378OH9B</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P000-202500000007515</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DTE-03-M001P001-000000000006471</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1P001-00000000000647106141511770020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Unilever El Salvador SCC S.A. de C.V.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B9A18830-BC40-4CCC-A69C-ECBD56BEF82F</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>20251011572B6BB14CE8B228F19B13376D04ALF5</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P000-202500000007516</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DTE-03-M001P001-000000000006473</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1P001-00000000000647306141511770020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Unilever El Salvador SCC S.A. de C.V.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>834568C3-C712-4B06-B29F-75712FE89D05</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025D24377497923445588CBDD14E9AF5A11GPQG</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P000-202500000007517</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DTE-03-M001P001-000000000006510</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1P001-00000000000651006141511770020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Unilever El Salvador SCC S.A. de C.V.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7F86893E-B4C4-43AC-BBB8-CB86B0F28252</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>202593FE9E19C96447D9A3C300867FE792B4VS3S</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P000-202500000007518</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DTE-03-M001P001-000000000006513</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1P001-00000000000651306141511770020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Unilever El Salvador SCC S.A. de C.V.</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>90178B90-0DA9-45DF-BA1D-22FF343E2EAC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025D01C2DD3C4BC4106B13728F6A593EDE7MFFX</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P000-202500000008377</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DTE-03-M001P001-000000000007244</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1P001-00000000000724406141511770020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MEDRANO FLORES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>264724A6-8A93-4752-97A5-1AAC6AE3719B</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025269B3F6B108B4CDBA2ED02BDD6E966FFEE8T</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000007183</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>21D0B3C4-DC41-4AAC-9BD4-51A36B490AC0</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>25.68</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>264724A6-8A93-4752-97A5-1AAC6AE3719B.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MEDRANO FLORES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>269A17A2-4029-4487-B494-F488358DDF5E</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025ED3D1FD2F70243F3B1416CF2AB37C0E6E5MX</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000006892</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BAAE81D4-56E4-4B8F-B925-6A4139E9460F</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>269A17A2-4029-4487-B494-F488358DDF5E.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TEXTUFIL, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>27E379B7-1B83-4C64-ADC0-5C83806A597A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>20257FC6851A0AD8441BB732299BA02A244EU86L</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P029-000000000006936</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>5EAED4FA-A270-4094-BCED-50687BCD34DB</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>27E379B7-1B83-4C64-ADC0-5C83806A597A.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TEXTUFIL, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>283B5113-C01B-46D1-A890-CD00F9A8E2F8</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>20252FA3EFE0657D43BA8C16447610676C9DXVUJ</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P029-000000000006440</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1034913E-0093-4E2C-BAC7-D89B58AB7F48</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>283B5113-C01B-46D1-A890-CD00F9A8E2F8.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CALLEJA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2A7845F5-10D0-4D23-9137-CDE526530AFE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>20253AB6B169834A46B6B45939D6C17692A20SFT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000012010</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>69FBBF11-054E-48A3-AADA-29AA1ED6034B</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2A7845F5-10D0-4D23-9137-CDE526530AFE.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CALLEJA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2A7845F5-10D0-4D23-9137-CDE526530AFE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>20253AB6B169834A46B6B45939D6C17692A20SFT</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000012010</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>E542894F-1373-433D-A0DF-8F1110676CE6</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2A7845F5-10D0-4D23-9137-CDE526530AFE.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CALLEJA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2A7845F5-10D0-4D23-9137-CDE526530AFE</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>20253AB6B169834A46B6B45939D6C17692A20SFT</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000012010</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>8E280078-A4FE-43A1-AE68-98A1B4E219F4</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2A7845F5-10D0-4D23-9137-CDE526530AFE.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CALLEJA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2A7845F5-10D0-4D23-9137-CDE526530AFE</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>20253AB6B169834A46B6B45939D6C17692A20SFT</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000012010</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>674E3AEE-306C-4A76-A071-641B5FBD7910</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2A7845F5-10D0-4D23-9137-CDE526530AFE.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CALLEJA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2A7845F5-10D0-4D23-9137-CDE526530AFE</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>20253AB6B169834A46B6B45939D6C17692A20SFT</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000012010</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>B19134CC-1318-4CC2-961B-DA838C63C8AF</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2A7845F5-10D0-4D23-9137-CDE526530AFE.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CALLEJA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2A7845F5-10D0-4D23-9137-CDE526530AFE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>20253AB6B169834A46B6B45939D6C17692A20SFT</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000012010</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>A5DADDD6-1446-4E18-9CF7-1B10C68FC004</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2A7845F5-10D0-4D23-9137-CDE526530AFE.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CALLEJA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2A7845F5-10D0-4D23-9137-CDE526530AFE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>20253AB6B169834A46B6B45939D6C17692A20SFT</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000012010</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>CB259E2E-392C-4034-932B-56EFD05D7737</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2A7845F5-10D0-4D23-9137-CDE526530AFE.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MEDRANO FLORES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>397F2380-4487-4AD8-879A-8B21608BC008</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025D04C04F421D749D1B4EDF978A65BAB56JLCS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000007021</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>40420D7C-093D-4296-B2A6-6A8188B4E3F5</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>397F2380-4487-4AD8-879A-8B21608BC008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MERCADOS ELECTRICOS DE CENTROAMERICA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3F66EE72-42CE-429A-ADD7-479231E99B71</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025F9CF8C97999F4E2FB8CB57FBC719F380T0PB</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P000-000000000000224</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>A5E9ED8E-38B4-4647-A426-F5193E9CF79A</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3F66EE72-42CE-429A-ADD7-479231E99B71.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>COMISIÓN EJECUTIVA HIDROELÉCTRICA DEL RÍO LEMPA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0EBE3379-5203-1FE0-ADD3-740CCEDA8FC5</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>202582E9F7AFD9E34DCC85123083F97BB14DORL2</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>43043AD5-35CE-4FCF-E064-00144FF8838D</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025F36E5F8622B644CFB7B0138AEC280E1CWKB8</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P000-000000000004642</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>643A75E9-763A-4D78-B8E1-8E1FDC72871D</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>43043AD5-35CE-4FCF-E064-00144FF8838D.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>COMISIÓN EJECUTIVA HIDROELÉCTRICA DEL RÍO LEMPA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>43535047-9E86-17F6-E064-00144FF8838D</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025733648B889094DF6A294061279F8211EJOLV</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P000-000000000004676</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>BC3AE47E-EDCF-4A59-9DA4-0DEF4606D209</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>43535047-9E86-17F6-E064-00144FF8838D.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TEXTUFIL, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4F3DC115-3B92-4484-830F-BC316CED7AE6</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025AEF119D2F80141BEAB881A8DCFB1A592NZWY</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P029-000000000006449</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>05410E28-EDEF-4ED9-90F9-ABE9653658F9</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4F3DC115-3B92-4484-830F-BC316CED7AE6.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ingenio La Cabaña S.A. de C.V.</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>50500DA2-6BC8-4588-8F2A-36BF6F3D83A7</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>20255A4B30C830EA4568A7A363FC86DB31F1V4ZB</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>responseMH -&gt; selloRecibido</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>DTE-07-M001P000-000000000002115</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>6985</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>50.02</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Plycem_5100010374_2025.json</t>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-250000000005658</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>DTE03M001P001000000000007123</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50500DA2-6BC8-4588-8F2A-36BF6F3D83A7.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Rayones de El Salvador S.A. de C.V.</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>5261228E-5188-4F4C-8D03-B83CB26DFF85</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>202563AC26410D804A3AA5971C17DBE42EEB4AFH</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P004-000000000001434</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>FD7D485B-B79D-451F-A783-5E07742FAA0E</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5261228E-5188-4F4C-8D03-B83CB26DFF85.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>COMPAÑIA AZUCARERA SALVADOREÑA S.A DE C.V.</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-AEB2-808000245862</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025E7686EF4694944819613845B82916729V0HV</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000008676</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>496737519086</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-AEB2-808000245862.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>COMPAÑIA AZUCARERA SALVADOREÑA S.A DE C.V.</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-AEB2-828000245863</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>20251E79D7A7EE8A461A8562F1CFE8E411FFNKH6</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000008677</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>EAF4980B126E</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-AEB2-828000245863.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>COMPAÑIA AZUCARERA SALVADOREÑA S.A DE C.V.</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B09C-A98000246506</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025957C1C6555984813818E8DC547E0684DYQCK</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000008996</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>F2653ABEC4F9</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B09C-A98000246506.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>COMPAÑIA AZUCARERA SALVADOREÑA S.A DE C.V.</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B09C-AE8000246507</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>20251C3CB97C65A8450B8C8BDFE520A2AC5FUMHV</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000008997</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>7A8319D186E7</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B09C-AE8000246507.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>COMPAÑIA AZUCARERA SALVADOREÑA S.A DE C.V.</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B09C-B28000246508</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>20255C3200D52AC1430489E522CE21A4FD675HDD</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000008998</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>4740CCF8828A</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B09C-B28000246508.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>COMPAÑIA AZUCARERA SALVADOREÑA S.A DE C.V.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B1B0-E68000246623</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025553AD9538819484BB6E093077C99D86FHDZO</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000009099</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>3B2C267AD7F4</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B1B0-E68000246623.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>COMPAÑIA AZUCARERA SALVADOREÑA S.A DE C.V.</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B1B1-C68000246695</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025F0DDD70C096248F9900D1A8024ABFC56E2LF</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000009170</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>5D4378106E63</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B1B1-C68000246695.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>COMPAÑIA AZUCARERA SALVADOREÑA S.A DE C.V.</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B393-538000247174</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>202509A17D145EA14C07AB4E6068455A1707AZWJ</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000009431</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>79B16578D517</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B393-538000247174.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>COMPAÑIA AZUCARERA SALVADOREÑA S.A DE C.V.</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B393-568000247175</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025DC97AA52E90549158117EE5F170B3771I4IB</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000009432</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>D56D0E4A2308</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B393-568000247175.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>INGENIO CHAPARRASTIQUE, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B395-6B8000247295</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025D62FBEE8082349C49686E025C712A2BDY6UV</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000004693</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>9BB4EB7708E5</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B395-6B8000247295.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>INGENIO CHAPARRASTIQUE, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B395-6E8000247296</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025233E960E91DE48A79036252C384514E3DDO3</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000004694</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>6AAB19783B71</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>7</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B395-6E8000247296.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>INGENIO CHAPARRASTIQUE, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B395-708000247297</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025B2F1A871CAB6432F841DC6DD60F7FC4FLHFZ</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000004695</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>F05075AB3E2B</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B395-708000247297.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>INGENIO CHAPARRASTIQUE, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B395-738000247298</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>202587CF85BF63A640CAA013C982CE6044999J2N</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000004696</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>A05818319836</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>7</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B395-738000247298.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>INGENIO CHAPARRASTIQUE, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B395-758000247299</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025FAF55636CC994670859A16552B0904BEVPZV</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000004697</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>4796487851ED</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>63995E65-FA18-1FD0-B395-758000247299.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CENTRAL DE RODAMIENTOS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>6F3EC5DD-FE11-4A56-ABF8-5052DDFAADDD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>20251F014316520842EA9CCCAB4DEB6A1FBCSDOU</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>DTE-05-M001P001-000000000000371</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6F3EC5DD-FE11-4A56-ABF8-5052DDFAADDD.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Rayones de El Salvador S.A. de C.V.</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>71954747-81F4-4FBE-BF8F-4B8B171FECF1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>20255F6D0172EB3C449B9BF4A4EC57101FF3UWNS</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P004-000000000001531</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2FFDFA99-AD06-47BA-AF0F-7486E6DB40F1</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>71954747-81F4-4FBE-BF8F-4B8B171FECF1.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TEXTUFIL, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>79157784-11AD-4903-B5F6-EB9A39E20377</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>20256D507C09C9F547D4BE3628FB5D4D5AC8ZCKB</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P029-000000000006630</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>6A3CDD12-05F2-4223-8B78-6DBC322C4DBC</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>79157784-11AD-4903-B5F6-EB9A39E20377.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MEDRANO FLORES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>7D41829A-DE48-4C50-9030-B192AF151C77</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>20254C725F95977F46F5A3C8ED3425EB0FADQOQ1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000007024</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>E6C5EF48-58DE-40A9-9AF1-645051F98E6B</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7D41829A-DE48-4C50-9030-B192AF151C77.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TEXTUFIL, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>80A7EEC7-577E-4D91-8401-2689379D89C4</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025BD7984BB1FEE4F70953EB1EEEA07A31FEVWO</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P029-000000000006631</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1EFA2D27-AB3D-4865-9BC2-2D2F662B4EBD</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>80A7EEC7-577E-4D91-8401-2689379D89C4.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>RUA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>83CF9CF3-7D3A-4352-B3BA-72BCA15BF460</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>sello</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-202500000000942</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>DTE2025-7153</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>83CF9CF3-7D3A-4352-B3BA-72BCA15BF460.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DE LA PEÑA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>86B872B3-7509-4495-9187-4279F27A1B2D</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>202528ED08244CA9477A9F17E3F0FB53D499HMQE</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P002-000000000001054</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>8CDA6757-2EBB-4A34-B292-01E639525200</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>86B872B3-7509-4495-9187-4279F27A1B2D.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MEDRANO FLORES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>888A968D-CE20-41EE-87F2-D6F70A9FB151</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>20255B4E6B5492724A8487D9FC2F49DA9DC0AKDJ</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000006494</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1A81600C-D0A4-4CBB-B4FF-0E8ACADBE927</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>888A968D-CE20-41EE-87F2-D6F70A9FB151.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Cartonera Centroamericana, S.A. de C.V.</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>8D4912C3-3972-1FE0-B3B2-C2ACA286BCB7</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>20258F43F419F15442CC90F33970FA9CB2A4IW5P</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000001152</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>DTE-03-7521</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>8D4912C3-3972-1FE0-B3B2-C2ACA286BCB7.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Cartonera Centroamericana, S.A. de C.V.</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>8D4912C3-3972-1FE0-B3B2-C2ACA286BCB7</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>20258F43F419F15442CC90F33970FA9CB2A4IW5P</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000001152</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>DTE-03-7232</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>8D4912C3-3972-1FE0-B3B2-C2ACA286BCB7.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TEXTUFIL, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>8D963F4A-24DB-43CB-A4FC-B8B129B6152F</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>202511A9358AEA344A1BABBFC10B17B00C66IX2B</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P029-000000000006666</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>67223B8C-C6C1-4D25-A454-6AB23D50F408</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>8D963F4A-24DB-43CB-A4FC-B8B129B6152F.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CENTRAL DE RODAMIENTOS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>9C610C5D-92C9-4FE2-8C7F-578AC90854A9</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>20258417EA498FF84234B3D321A20ADC7501U6ZS</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>DTE-03-M001P001-000000000007812</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>9C610C5D-92C9-4FE2-8C7F-578AC90854A9.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TEXTUFIL, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>A3D11227-70B9-4D40-81E5-8901ABF6A766</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>20255EA680896F574307AA13F1161313A2E4DHFB</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P029-000000000006439</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>A7FF5C77-589C-462C-BC13-05C5DAC93C40</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>A3D11227-70B9-4D40-81E5-8901ABF6A766.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CONDUSAL, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>A46D4E64-4485-41B4-8248-152D2E98DD72</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2025716F05B7E49D46A9980FDD7F878562B4I2RK</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000001483</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>45B5554E-FBB2-4CAB-8906-C601DEE0EA07</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>A46D4E64-4485-41B4-8248-152D2E98DD72.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MOLINOS DE EL SALVADOR, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ABF1227C-1FCA-43A4-817B-DB4D94FEAF04</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2025DF9666BF7038489B9535F5A5B08A3572SDEU</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000005112</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>4ECC5873-83C9-4142-9605-187F0E2F9CEB</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>ABF1227C-1FCA-43A4-817B-DB4D94FEAF04.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>RESORTES Y ALAMBRES, LTDA DE C.V.</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AF03CD2B-9D09-4F97-80E8-7AB66E843F99</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>20254DAA15BE853C481DAE709BB5432B43ECUKPR</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000001257</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>AEFC71C8-327C-46F3-AE90-B7B43F11957B</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>AF03CD2B-9D09-4F97-80E8-7AB66E843F99.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MEDRANO FLORES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>B52270FA-58B8-472D-AE09-355D447A5CF2</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2025A9136E09A72E4FADA25D7AC1025445CEKCBI</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000006778</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>C487C262-D03B-4319-BE35-48F565F6CEDF</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>B52270FA-58B8-472D-AE09-355D447A5CF2.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TEXTUFIL, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>B73C67D4-F513-4199-8329-4B1062067E81</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>202577B4DE0556F74B1DA3E2AAAE144AF339Y9ZB</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P029-000000000006638</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>37B54731-1B52-4407-AE60-FECCC327BC74</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>B73C67D4-F513-4199-8329-4B1062067E81.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CENTRAL DE RODAMIENTOS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>C205B00E-A61F-476F-AEBE-81E97844A178</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025AD8087A2211F405D90C2777C9507A7B8GFLI</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>DTE-03-M001P001-000000000007704</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>C205B00E-A61F-476F-AEBE-81E97844A178.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ECO FOODS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>C5D598D6-0748-4E1A-B57E-4B35189EBBF4</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025B243466F32494C47B2A266D14E1C7972ENIR</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000001061</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>871B748E-509E-4E94-9AD9-76552DA98410</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>C5D598D6-0748-4E1A-B57E-4B35189EBBF4.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MEDRANO FLORES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>C6E2AB93-65FA-4E40-AC6E-59AE8CC63431</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025A77CF1C194F04295B26E435D8C0671EEVG1Q</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000007182</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>E3C6F01A-18A9-4F2A-BFA2-4A9CFE55DE64</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>38</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>C6E2AB93-65FA-4E40-AC6E-59AE8CC63431.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Rayones de El Salvador S.A. de C.V.</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>CA105E91-D16E-40A5-BF95-76BF0E5A8C84</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>202533171AC5330D47E7B66D59929EC377DFLNYY</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P004-000000000001451</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>B58F50D5-A0E2-47C0-A4E2-89A3C9D37991</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>CA105E91-D16E-40A5-BF95-76BF0E5A8C84.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>CENTRAL DE RODAMIENTOS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>D39DC43D-2750-460B-8EFF-ECAAB9CA66DC</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>202595375BAFD0C8489C8E544ACA26527545E37N</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>DTE-03-M001P001-000000000007811</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>D39DC43D-2750-460B-8EFF-ECAAB9CA66DC.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TEXTUFIL, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>D6B39A84-23B5-407E-B820-B292D1D152A0</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2025E624F8E853AA469FAFBB4B621D6585732USA</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P029-000000000006814</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>A5690804-7C32-4028-96CA-C58C7EEFDAC5</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>D6B39A84-23B5-407E-B820-B292D1D152A0.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CENTRAL DE RODAMIENTOS, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>D9D08459-A210-4E50-B4D4-A15AF613CBD5</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>20250337472888A94AC486DA240E3EAFD960YGCO</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>DTE-03-M001P001-000000000007653</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>D9D08459-A210-4E50-B4D4-A15AF613CBD5.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DE LA PEÑA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>202590448BDAA86A4D25A6F40EA4B3C45C0DLG2R</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P002-000000000001181</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>4D558DE1-62A9-46D6-9DC6-6A8120A485AF</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>DE LA PEÑA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>202590448BDAA86A4D25A6F40EA4B3C45C0DLG2R</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P002-000000000001181</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>B28377CD-04ED-41D5-BE67-E1C30C5F2A0A</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>DE LA PEÑA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>202590448BDAA86A4D25A6F40EA4B3C45C0DLG2R</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P002-000000000001181</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>D59AFDC5-E4DF-461F-AF6C-39FD1CA0A1B3</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DE LA PEÑA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>202590448BDAA86A4D25A6F40EA4B3C45C0DLG2R</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P002-000000000001181</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>9F8F173A-63DC-4921-B42C-33D1637F5A55</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>DE LA PEÑA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>202590448BDAA86A4D25A6F40EA4B3C45C0DLG2R</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P002-000000000001181</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1D65F344-AD5C-4F05-BC5C-D01DB181243E</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>DE LA PEÑA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>202590448BDAA86A4D25A6F40EA4B3C45C0DLG2R</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>responseMH -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P002-000000000001181</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2AD4FBC3-82BF-42AB-A6C7-C5D16A327F82</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>DA4D4B01-C7FA-4878-8DA7-A89B72DC29C6.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TEXTUFIL, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DC7C7B8F-1405-49F7-AA31-A4AAFBC87EBE</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>202596ECB21F0F6F49AD80C0E5418C956632ORBD</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P029-000000000006601</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>33344927-008B-42A5-87AC-324FBFCD4244</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>DC7C7B8F-1405-49F7-AA31-A4AAFBC87EBE.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CORPORACION INDUSTRIAL CENTROAMERICANA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2F1B8414-99C9-4277-B970-CB1C8B14B12C</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010170</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>DTE-7354</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010170-2F1B8414-99C9-4277-B970-CB1C8B14B12C-10-11-2025 025523.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>CORPORACION INDUSTRIAL CENTROAMERICANA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>9D020BB0-D298-4819-83AC-BEE2E40939CB</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010461</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>DTE-7506</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>16</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010461-9D020BB0-D298-4819-83AC-BEE2E40939CB-18-11-2025 021735.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CORPORACION INDUSTRIAL CENTROAMERICANA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AEFC8F20-D47A-4EE3-AF07-A6AC06B88CF8</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010550</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>DTE-7600</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010550-AEFC8F20-D47A-4EE3-AF07-A6AC06B88CF8-20-11-2025 024901.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>CORPORACION INDUSTRIAL CENTROAMERICANA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>27B0CB09-4F1C-4604-8E57-795B04E582B6</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010707</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>DTE-7661</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010707-27B0CB09-4F1C-4604-8E57-795B04E582B6-25-11-2025 101502.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CORPORACION INDUSTRIAL CENTROAMERICANA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>27B0CB09-4F1C-4604-8E57-795B04E582B6</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010707</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>DTE-7670</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010707-27B0CB09-4F1C-4604-8E57-795B04E582B6-25-11-2025 101502.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CORPORACION INDUSTRIAL CENTROAMERICANA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>29029575-E3E0-4DD9-BE43-5ABCA1C0F71A</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010770</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>DTE-7648</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010770-29029575-E3E0-4DD9-BE43-5ABCA1C0F71A-26-11-2025 022548.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CORPORACION INDUSTRIAL CENTROAMERICANA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>29029575-E3E0-4DD9-BE43-5ABCA1C0F71A</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010770</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>DTE-7647</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010770-29029575-E3E0-4DD9-BE43-5ABCA1C0F71A-26-11-2025 022548.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CORPORACION INDUSTRIAL CENTROAMERICANA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>29029575-E3E0-4DD9-BE43-5ABCA1C0F71A</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010770</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>DTE-7646</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010770-29029575-E3E0-4DD9-BE43-5ABCA1C0F71A-26-11-2025 022548.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CORPORACION INDUSTRIAL CENTROAMERICANA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>359910A9-A847-4F1C-88D2-A6CF961A9E52</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010871</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>DTE-7776</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010871-359910A9-A847-4F1C-88D2-A6CF961A9E52-28-11-2025 024944.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>CORPORACION INDUSTRIAL CENTROAMERICANA, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>359910A9-A847-4F1C-88D2-A6CF961A9E52</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010871</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>DTE-7779</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P010-000000000010871-359910A9-A847-4F1C-88D2-A6CF961A9E52-28-11-2025 024944.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>INMUEBLES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>EC2A892C-5336-49BE-832F-4D2656FA682E</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2025FFDFD98966234EF8815BF804042CBC70NEN7</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000001648</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>4CF1AF11-10E9-4EB6-AC98-FA9C14BD086B</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>EC2A892C-5336-49BE-832F-4D2656FA682E.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>MEDRANO FLORES, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>EFA27456-B005-4F04-A1FD-EB72617BC038</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2025F1ACB2DEEBCC4272ACE134856D51F1B6L4ZW</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000006900</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>79B9FC1B-4AF3-4EC4-B7D9-EB357255A187</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>EFA27456-B005-4F04-A1FD-EB72617BC038.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TEXTUFIL, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>F9EA6881-4E9A-40B9-B307-3C6213F4D3F8</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2025CF6DC3CEEC8847FBA8B2970B0C3CC269CPBX</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P029-000000000006594</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>13558846-161F-40B8-9157-1B2B187DF6B9</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>F9EA6881-4E9A-40B9-B307-3C6213F4D3F8.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Rayones de El Salvador S.A. de C.V.</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>FC71A4F2-606A-4C12-968B-1C3F3F13E0E1</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>202500DF47A0211F4F078F6DC48D00D42669WZR9</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P004-000000000001452</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>45984FC7-6E4B-4F7D-8558-4FFDF8194EF5</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>FC71A4F2-606A-4C12-968B-1C3F3F13E0E1.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AGROINDUSTRIAS SAN JULIAN SA DE CV</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>FDFD466B-597B-4483-B341-C24123BC9ED9</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2025A4CBD2C6CDCF4B5FBF90F7516200ED54UU0X</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>selloRecibido</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>DTE-07-S002P001-000000000005034</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>CA5180D5-D2A3-49E4-8AC1-3BE473FF246C</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>FDFD466B-597B-4483-B341-C24123BC9ED9.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>IMPRESORA LA UNION, S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>18943ADD-5464-4A08-BB9F-31828E9E1521</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>20259B02454642F44C569B8AD2AAA91CE9253D06</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>respuestaHacienda -&gt; selloRecibido</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>DTE-07-M001P001-000000000003384</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>814643A4-FBC3-403B-A4EF-FE1A58FC31EC</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Retención No.4999.json</t>
         </is>
       </c>
     </row>
